--- a/data/export_data.xlsx
+++ b/data/export_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,136 +436,969 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@numberone1700/video/7675410277822631189</t>
+          <t>https://www.tiktok.com/@sungvotrine/video/7677466118923554068</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Menu migul bắn sinh tồn cực đã</t>
+          <t>Sừng Vô Tri Giả BOT Bị Khịa và Cái Kết Nè..?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>#highlightff #freefire #fyb #migul #garenafreefire</t>
+          <t>#sungvotri #freefire #garenafreefire</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@numberone1700/video/7676524800310840596</t>
+          <t>https://www.tiktok.com/@sungvotrine/video/7677374641714892052</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>cầm menu migul cân 4 trong rank sinh tồn</t>
+          <t>Sừng Vô Tri Tạo Quân Đoàn..?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>#highlightff #freefire #fyb #migul #garenafreefire</t>
+          <t>#sungvotri #freefire #garenafreefire</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@numberone1700/video/7673555718154276116</t>
+          <t>https://www.tiktok.com/@sungvotrine/video/7677071408660237588</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>đừng ảo cân 4 khi chưa có menu migul</t>
+          <t>Sừng Vô Tri Bất Ngờ Gặp Thanh Niên Lướt Ván Bắn Cực Ảo Nè..!</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>#highlightff #freefire #fyb #migul #garenafreefire</t>
+          <t>#sungvotri #freefire #garenafreefire</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@numberone1700/video/7672072573538159893</t>
+          <t>https://www.tiktok.com/@sungvotrine/video/7677157770247900436</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>menu gì mà bá quá đii</t>
+          <t>Sừng Vô Tri Giả BOT bị Địch Khịa Và Cái Kết Nè..?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>#highlightff #freefire #fyb #migul #garenafreefire</t>
+          <t>#sungvotri #freefire #garenafreefire</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@numberone1700/video/7669846781710257428</t>
+          <t>https://www.tiktok.com/@sungvotrine/video/7676706234023775508</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nhiều ngày dài trông ngóng migul</t>
+          <t>Sừng Vô Tri [ HACK hay là KỸ NĂNG..? ]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>#freefire #highlightff #fyb #migul #garenafreefire</t>
+          <t>#sungvotri #freefire #garenafreefire</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@numberone1700/video/7670595737574477076</t>
+          <t>https://www.tiktok.com/@sungvotrine/video/7676632818964794644</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lang thang đi tìm migul leo top</t>
+          <t>Sừng Vô Tri Giả Vờ Bắn Ngu Rồi Cân 4 Xem Phản Ứng Của Đồng Đội Nè..?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>#highlightff #freefire #fyb #migul #garenafreefire</t>
+          <t>#sungvotri #freefire</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@numberone1700/video/7674668914038557973</t>
+          <t>https://www.tiktok.com/@sungvotrine/video/7677014733366643988</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Menu migul giải đáp thắc mắc</t>
+          <t>Sừng Vô Tri Bất Ngờ Gặp Được Bạn Fan Nhỏ Siêu Dễ Thương Nè..!</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>#highlightff #freefire #fyb #migul #garenafreefire</t>
+          <t>#sungvotri #freefire #garenafreefire</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@numberone1700/video/7669475070162636053</t>
+          <t>https://www.tiktok.com/@sungvotrine/video/7676329390749289748</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tất cả các e đã bị menu migul a bao vây</t>
+          <t>Sừng Vô Tri Thử Cân 4 Bằng Lục Bạc Bị Đồng Đội Khinh Thường Và Cái Kết Nè..?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>#freefire #highlightff #fyb #migul #garenafreefire</t>
+          <t>#sungvotri #freefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7676256690999725333</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri Giả BOT rồi Cân 4 xem Phản Ứng của Đồng Đội Nè..!</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7676429564515568917</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri Gặp Fan trong Trận và Cái Kết Nè..?</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7676069296652717332</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri Thử Giả HACK Cân 4 Xem Phản Ứng Của Đồng Đội Nè..?</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7675886198870592788</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Thử Mặc Bộ Đồ Bảo Vệ Cân 4 Xem Phản Ứng Của Đồng Đội Nè..?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>#freefire #sungvotri #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7675599376122907924</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tạm Biệt Free Fire..!</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #garenafreefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7675952889029790997</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri Thử để Đồng Đội Chết Hết rồi Cân 4 xem Phản Ứng Nè</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7675666314555378965</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Đây là HACK hay là Kỹ Năng 🤔..?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #garenafreefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7675300655396949269</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sừng Thử Cân 4 Đầu Game và Cái Kết..?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire #garenafreefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7675220929718373652</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HACK hay Kỹ Năng..?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire #garenafreefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7675141889330351380</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sừng Zô Tri Solo với Gái và Cái Kết Nè..?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire #garenafreefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7675513354437283093</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Thanh Niên Khịa Súng 7 Sừng Vô Tri và Cái Kết..?</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7674843433583824148</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri Chơi Với Bạn Nhỏ Dễ Thương Nè 🥰..!</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7674771873309248788</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sừng Zô Tri Bất Ngờ Được Đồng Đội Cho Súng Nè..!</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7674561098552626452</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sừng bất ngờ gặp HACK khi đang leo rank Đầu Mùa Nè 😡</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7674463646378020116</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri Tặng Quà Sinh Nhật cho Bạn Fan Nhỏ Nè 🥰</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7674145122363182356</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>[ Phần 2 ] Sừng Vô Tri Giả BOT đi Kênh Thế Giới Nè 🥰</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7674413971507662100</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Phản Ứng của 1 Fan Nhỏ khi Gặp Sừng Vô Tri Nè..!</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7674942981576707349</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri Bất Ngờ Bị Khịa Súng 7 trong Đảo Kết Nối Nè..!</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>#freefire #sungzotri #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7674090752187567381</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>[ Phần 3 ] Làm quen với Bạn Nữ trong Độc Lang Chiến Nè..!</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7673865659599621396</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>[ Phần 2 ] Làm quen với Bạn Nữ trong Độc Lang Chiến Nè..!</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7674042407935102228</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>[ Phần 2 ] Sừng gặp Idol Live TT trong Đảo Kết Nối Nè 🥰</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7673802055026232597</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>[ Ngày 24 ] Sừng Thử làm Quen Gái trong Độc Lang Chiến Nè</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>#freefire #sungvotri #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7673732217650056468</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri Bất Ngờ Gặp Các Top Sever Sinh Tồn Nè 🥶😱..!</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7673660171633134869</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>[ Phần 2 ] Gặp Thanh Niên Trẻ Trâu Khịa Súng 7 trong ĐKN..!</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7673287852972674325</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri Gặp Bạn Fan Nhỏ Nè..! 🥰</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7673367721752448277</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri Bất Ngờ Gặp Bạn Nhỏ Siêu Thương và Nói Nhiều 😅</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7673057845914406165</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri thử mặc đồ BOT đi kênh thế giới Nè 🥰..!</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7672974282925886740</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sừng Zô Tri bất ngờ gặp Bạn Fan Dễ Thương trong Đảo Kết Nối..!</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7673430735604174101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri bị Trẻ Trâu Khịa súng 7 trong Đảo Kết Nối..?</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7672768500783385876</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sừng Zô Tri hướng dẫn phối đồ 7 Đá Nè..!</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7672711676231175444</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>[ Ngày 23 ] Làm Quen Với Phú Bà trong Đảo Kết Nối..!</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7672917951045012757</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kiếp Nạn leo góc Lag trong Đảo Kết Nối của Sừng Zô Tri Nè..!</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7672662128658025748</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>[ Ngày 22 ] Làm quen với 2 Bạn Nữ siêu Đáng Yêu nè..!</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #nhasangtaofreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7672550951349128468</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Có Bạn nào đã trải qua cái Cảm Giác này chưa..?</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7672292032521489684</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>[ Phần 2 ] Làm Quen với Thanh Niên VIP 8 Bốc Phét..!</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7672222804627983637</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>[ Phần 2 Ngày 16 ] Làm Quen với Bạn Nữ 2k14 trong Đảo Kết Nối..!</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7672172710918753556</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>[ Ngày 16 ] Làm quen với Bạn Nữ 2k14 trong Đảo Kết Nối..!</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7672607825729785109</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>[ Ngày 21 ] Làm quen với bạn Nữ k12… Thất Bại</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7671982659647720725</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri bị Thanh Niên VIP 8 Gạ Solo hành động Súng 7..!</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #garenafreefireeindonesia #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7672339832978361621</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Sừng Vô Tri gặp Bạn Nam Nhỏ Dễ Thương trong Đảo Kết Nối Nè..!</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7671870156733189396</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>[ Phần 2 Ngày 3 ] Làm Quen với Bạn Nữ K11 trong Đảo Kết Nối</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7671809189299227924</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>[ Ngày 3 ] Làm Quen với Bạn Nữ Siêu Đáng Yêu trong Đảo Kết Nối</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7671921634105675029</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>[ Phần 3 / Ngày 3 ] Làm Quen Với Bạn Nữ Siêu Đáng Yêu K11</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7671608455626657045</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>[ Ngày 2/ Phần 2 ] Làm Quen với Bạn Nữ Siêu Dễ Thương trong Đảo Kết Nối</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7671477904898854165</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>( Phần 2 ) Làm Quen Bạn Nữ 2k9 Trong Đảo Kết Nối…</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7671424430253313300</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Hành trình 100 Ngày làm Quen với 100 Bạn Nữ trong Đảo Kết Nối ( Ngày 1 )</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7671224935712296213</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>[ Phần 2 Ngày 15 ] Làm quen với Bạn Nữ Vip 8 Dễ Thương..!</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7671184305183395092</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>[ Ngày 15 ] Làm quen với Bạn Nữ VIP 8 trong Đảo Kết Nối…!</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>#sungvotri #freefire #garenafreefire</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@sungvotrine/video/7671512230202051860</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>[ Ngày 2 ] Làm Quen với Bạn Nữ Siêu Dễ Thương Trong Đảo Kết Nối</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>#sungzotri #freefire</t>
         </is>
       </c>
     </row>

--- a/data/export_data.xlsx
+++ b/data/export_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,51 +436,1700 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7539241693518843137</t>
+          <t>https://www.tiktok.com/@maryen1134/video/7679816805514300692</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>✈️✈️✈️</t>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 183 lesson</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>#lionchampionship2025 #NationalPride #LIONchampionship #LC25 #MMADUO</t>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7676886184445971720</t>
+          <t>https://www.tiktok.com/@maryen1134/video/7679810917592304916</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chia sẻ của Trần Ngọc Lượng sau trận đấu với Emunanjia</t>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 182 lesson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>#LIONChampionship #YFU96 #YFUxLION #TheLIONEra</t>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@lionchampionshipvietnam/video/7676876479883463943</t>
+          <t>https://www.tiktok.com/@maryen1134/video/7679798841440374036</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dù giành chiến thắng, nhưng Emunanjia vẫn phải chịu không ít tổn thương sau trận đấu với TNL 🤕</t>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 181 lesson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>#LIONChampionship #YFU96 #YFUxLION #TheLIONEra</t>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7679794903945088277</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 179 lesson</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7679076846461406484</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 178 lesson</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7678731433627716884</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 175 lesson</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7679067900094713109</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 177 lesson</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7679065532800224532</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 176 lesson</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7678711326650174740</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 173 lesson</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7678721073034071316</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 174 lesson</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7678325361863576852</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 172 lesson</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7679798289482517780</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 180 lesson</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7677967180776049941</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 168 lesson</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7677976411524713748</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 169 lesson</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7677960370497080597</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 167 lesson</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7677529396558728468</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 165 lesson</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7677524939234200853</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 164 lesson</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7678641489135652117</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 170 lesson</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7677593288035028244</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 166 lesson</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7677121037510659349</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 163 lesson</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7678324753731833108</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 171 lesson</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7677113345157221652</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 162 lesson</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7676747873890995476</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 160 lesson</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7676723208917241108</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 159 lesson</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7677112645610196245</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 161 lesson</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7676718812649114900</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 158 lesson</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7676350071889333525</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 157 lesson</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7676343628414995732</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 155 lesson</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7675960762791103764</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 153 lesson</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7675991777706413333</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 154 lesson</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7676344314888277269</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 156 lesson</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7675590067557092628</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 150 lesson</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7675959992939220245</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 152 lesson</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7675593395854658836</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 151 lesson</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7675589503502830869</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 149 lesson</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7675251915822845204</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 148 lesson</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7675251068237827349</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 147 lesson</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7675238139794853140</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 145 lesson</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7675237484682759444</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 144 lesson</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7675250279163563285</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 146 lesson</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7675236768819514645</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 143 lesson</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7674888547974909191</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 142 lesson</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7674990888099056903</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 139 lesson</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7674821810608884999</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 137 lesson</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7674822565709253896</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 138 lesson</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7674564490700082440</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 134 lesson</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7674638107752369415</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 136 lesson</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7674565181413805330</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 135 lesson</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7674887294356114696</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 140 lesson</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7674194857165868306</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 133 lesson</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7674887884264033554</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 141 lesson</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7674189934483279122</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 131 lesson</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7674190747322551570</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 132 lesson</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7673926770948721938</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 130 lesson</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7673923208407436562</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 129 lesson</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7673922333614165256</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 128 lesson</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7672857830797462792</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 115 lesson</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7672834558970088722</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 111 lesson</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7672849341899476242</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 114 lesson</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7672842893802884359</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 113 lesson</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7672841681472900370</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 112 lesson</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7672791027291344136</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 109 lesson</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7672833845414153490</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 110 lesson</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7672782781809708296</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 107 lesson</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7671984571000343815</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 106 lesson</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7671984126039198994</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 105 lesson</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7672786959072316690</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 108 lesson</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7671983374038289682</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 103 lesson</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7671715022665469191</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 99 lesson</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7671694270062955784</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 100 lesson</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7671983754230942994</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 104 lesson</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7671982624700747016</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 101 lesson</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7671983011633745159</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 102 lesson</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7671278347099442439</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 97 lesson</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7671690425954028807</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 98 lesson</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7671277252721642759</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 95 lesson</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7670958296794287368</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 94 lesson</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7670596233651588360</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 90 lesson</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7670595977824292104</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 89 lesson</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7670957145189354760</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 93 lesson</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7670596547817573640</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 91 lesson</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7670956855170043143</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 92 lesson</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7671277543600819464</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 96 lesson</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7670241587418516743</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 88 lesson</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7669854508108877064</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 84 lesson</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7670241023024467208</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 86 lesson</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7670241294408600840</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 87 lesson</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7669854260422790418</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 83 lesson</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7669101157406575893</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 79 lesson</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7669444504889593108</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 80 lesson</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7669445093144710420</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 82 lesson</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7669854789236296967</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 85 lesson</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7669444794246122772</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 81 lesson</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7668777162589228308</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 76 lesson</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7669100451861646612</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 77 lesson</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7668748096649694484</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 75 lesson</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7668747432515095828</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 74 lesson</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7669100737107971349</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 78 lesson</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7668363227499138325</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 73 lesson</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@maryen1134/video/7668362917724638485</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tiếng Anh giao tiếp hàng ngày 🗣️ | Post 72 lesson</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>#englishlistening #learnenglish #english #shadowing #englishlesson</t>
         </is>
       </c>
     </row>
